--- a/CALCOLI/2025_01_06_Particelle_Guidonia+QUOTE_SUCCESSIONE.xlsx
+++ b/CALCOLI/2025_01_06_Particelle_Guidonia+QUOTE_SUCCESSIONE.xlsx
@@ -497,7 +497,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -822,14 +822,6 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -870,7 +862,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -882,19 +874,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -906,15 +906,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -966,7 +962,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -990,11 +986,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -16272,16 +16268,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="78" width="10.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="78" width="7.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="78" width="14.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="81" width="9.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="19" style="82" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="83" width="18.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="21" style="81" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="18.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="81" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="78" width="9.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="19" style="79" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="81" width="18.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="21" style="78" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="18.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="78" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="84" t="s">
+    <row r="1" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
@@ -16302,19 +16298,19 @@
       <c r="G1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="85" t="s">
+      <c r="I1" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="85" t="s">
+      <c r="K1" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="83" t="s">
         <v>71</v>
       </c>
       <c r="M1" s="9" t="s">
@@ -16335,52 +16331,52 @@
       <c r="R1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="86" t="s">
+      <c r="S1" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="T1" s="87" t="s">
+      <c r="T1" s="85" t="s">
         <v>73</v>
       </c>
       <c r="U1" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="98" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="88" t="n">
+    <row r="2" s="97" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="90" t="n">
+      <c r="C2" s="88" t="n">
         <v>29</v>
       </c>
-      <c r="D2" s="90" t="n">
+      <c r="D2" s="88" t="n">
         <v>554</v>
       </c>
-      <c r="E2" s="90" t="n">
+      <c r="E2" s="88" t="n">
         <v>503</v>
       </c>
-      <c r="F2" s="90" t="s">
+      <c r="F2" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="90" t="n">
+      <c r="G2" s="88" t="n">
         <v>216.91</v>
       </c>
-      <c r="H2" s="91" t="n">
+      <c r="H2" s="89" t="n">
         <v>6840</v>
       </c>
-      <c r="I2" s="91" t="n">
+      <c r="I2" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J2" s="92" t="n">
+      <c r="J2" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K2" s="93" t="n">
+      <c r="K2" s="91" t="n">
         <f aca="false">(G2*I2)*160</f>
         <v>36440.88</v>
       </c>
-      <c r="L2" s="91" t="n">
+      <c r="L2" s="89" t="n">
         <f aca="false">(K2*P2)/100</f>
         <v>9110.22</v>
       </c>
@@ -16390,67 +16386,67 @@
       <c r="N2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="94" t="s">
+      <c r="O2" s="92" t="s">
         <v>26</v>
       </c>
       <c r="P2" s="28" t="n">
         <f aca="false">(100*2)/8</f>
         <v>25</v>
       </c>
-      <c r="Q2" s="95" t="n">
+      <c r="Q2" s="93" t="n">
         <f aca="false">P2/3</f>
         <v>8.33333333333333</v>
       </c>
       <c r="R2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="93" t="n">
+      <c r="S2" s="94" t="n">
         <f aca="false">L2</f>
         <v>9110.22</v>
       </c>
-      <c r="T2" s="96" t="n">
+      <c r="T2" s="95" t="n">
         <f aca="false">(K2*Q2)/100</f>
         <v>3036.74</v>
       </c>
-      <c r="U2" s="97"/>
-      <c r="W2" s="0"/>
+      <c r="U2" s="96"/>
+      <c r="W2" s="2"/>
     </row>
-    <row r="3" s="98" customFormat="true" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="88" t="n">
+    <row r="3" s="97" customFormat="true" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="86" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="99" t="n">
+      <c r="C3" s="98" t="n">
         <v>29</v>
       </c>
-      <c r="D3" s="99" t="n">
+      <c r="D3" s="98" t="n">
         <v>544</v>
       </c>
-      <c r="E3" s="99" t="n">
+      <c r="E3" s="98" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="99" t="n">
+      <c r="G3" s="98" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="91" t="n">
+      <c r="H3" s="89" t="n">
         <v>100</v>
       </c>
-      <c r="I3" s="91" t="n">
+      <c r="I3" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J3" s="92" t="n">
+      <c r="J3" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K3" s="93" t="n">
+      <c r="K3" s="99" t="n">
         <f aca="false">H3</f>
         <v>100</v>
       </c>
-      <c r="L3" s="91" t="n">
+      <c r="L3" s="89" t="n">
         <f aca="false">(K3*P3)/100</f>
         <v>25</v>
       </c>
@@ -16474,55 +16470,55 @@
       <c r="R3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="93" t="n">
+      <c r="S3" s="94" t="n">
         <f aca="false">L3</f>
         <v>25</v>
       </c>
-      <c r="T3" s="96" t="n">
+      <c r="T3" s="95" t="n">
         <f aca="false">(K3*Q3)/100</f>
         <v>8.33333333333333</v>
       </c>
-      <c r="U3" s="102" t="s">
+      <c r="U3" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="103"/>
+      <c r="W3" s="3"/>
     </row>
-    <row r="4" s="98" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="88" t="n">
+    <row r="4" s="97" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="86" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="90" t="n">
+      <c r="C4" s="88" t="n">
         <v>29</v>
       </c>
-      <c r="D4" s="90" t="n">
+      <c r="D4" s="88" t="n">
         <v>554</v>
       </c>
-      <c r="E4" s="90" t="n">
+      <c r="E4" s="88" t="n">
         <v>509</v>
       </c>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="90" t="n">
+      <c r="G4" s="88" t="n">
         <v>34.09</v>
       </c>
-      <c r="H4" s="91" t="n">
+      <c r="H4" s="89" t="n">
         <v>1074</v>
       </c>
-      <c r="I4" s="91" t="n">
+      <c r="I4" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J4" s="92" t="n">
+      <c r="J4" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K4" s="93" t="n">
+      <c r="K4" s="91" t="n">
         <f aca="false">(G4*I4)*160</f>
         <v>5727.12</v>
       </c>
-      <c r="L4" s="91" t="n">
+      <c r="L4" s="89" t="n">
         <f aca="false">(K4*P4)/100</f>
         <v>1431.78</v>
       </c>
@@ -16532,7 +16528,7 @@
       <c r="N4" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="94" t="s">
+      <c r="O4" s="92" t="s">
         <v>35</v>
       </c>
       <c r="P4" s="28" t="n">
@@ -16546,61 +16542,61 @@
       <c r="R4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="93" t="n">
+      <c r="S4" s="94" t="n">
         <f aca="false">L4</f>
         <v>1431.78</v>
       </c>
-      <c r="T4" s="96" t="n">
+      <c r="T4" s="95" t="n">
         <f aca="false">(K4*Q4)/100</f>
         <v>477.26</v>
       </c>
-      <c r="W4" s="0"/>
+      <c r="W4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="88" t="n">
+      <c r="A5" s="86" t="n">
         <v>6</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="90" t="n">
+      <c r="C5" s="88" t="n">
         <v>29</v>
       </c>
-      <c r="D5" s="90" t="n">
+      <c r="D5" s="88" t="n">
         <v>554</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="102" t="n">
         <v>517</v>
       </c>
-      <c r="F5" s="90" t="s">
+      <c r="F5" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="90" t="n">
+      <c r="G5" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="91" t="n">
+      <c r="H5" s="89" t="n">
         <v>465</v>
       </c>
-      <c r="I5" s="91" t="n">
+      <c r="I5" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J5" s="92" t="n">
+      <c r="J5" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K5" s="91" t="n">
+      <c r="K5" s="103" t="n">
         <v>465</v>
       </c>
-      <c r="L5" s="91" t="n">
+      <c r="L5" s="89" t="n">
         <f aca="false">(K5*P5)/100</f>
         <v>116.25</v>
       </c>
-      <c r="M5" s="105" t="s">
+      <c r="M5" s="104" t="s">
         <v>37</v>
       </c>
       <c r="N5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="94" t="s">
+      <c r="O5" s="92" t="s">
         <v>26</v>
       </c>
       <c r="P5" s="28" t="n">
@@ -16614,61 +16610,61 @@
       <c r="R5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="S5" s="93" t="n">
+      <c r="S5" s="94" t="n">
         <f aca="false">L5</f>
         <v>116.25</v>
       </c>
-      <c r="T5" s="96" t="n">
+      <c r="T5" s="95" t="n">
         <f aca="false">(K5*Q5)/100</f>
         <v>38.75</v>
       </c>
     </row>
-    <row r="6" s="98" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="88" t="n">
+    <row r="6" s="97" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="86" t="n">
         <v>9</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="90" t="n">
+      <c r="C6" s="88" t="n">
         <v>29</v>
       </c>
-      <c r="D6" s="90" t="n">
+      <c r="D6" s="88" t="n">
         <v>554</v>
       </c>
-      <c r="E6" s="90" t="n">
+      <c r="E6" s="88" t="n">
         <v>515</v>
       </c>
-      <c r="F6" s="90" t="s">
+      <c r="F6" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="90" t="n">
+      <c r="G6" s="88" t="n">
         <v>92.96</v>
       </c>
-      <c r="H6" s="91" t="n">
+      <c r="H6" s="89" t="n">
         <v>11718</v>
       </c>
-      <c r="I6" s="91" t="n">
+      <c r="I6" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J6" s="92" t="n">
+      <c r="J6" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K6" s="93" t="n">
+      <c r="K6" s="91" t="n">
         <f aca="false">(G6*I6)*160</f>
         <v>15617.28</v>
       </c>
-      <c r="L6" s="91" t="n">
+      <c r="L6" s="89" t="n">
         <f aca="false">(K6*P6)/100</f>
         <v>15617.28</v>
       </c>
-      <c r="M6" s="105" t="s">
+      <c r="M6" s="104" t="s">
         <v>38</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="94" t="s">
+      <c r="O6" s="92" t="s">
         <v>39</v>
       </c>
       <c r="P6" s="28" t="n">
@@ -16682,62 +16678,62 @@
       <c r="R6" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="S6" s="93" t="n">
+      <c r="S6" s="94" t="n">
         <f aca="false">L6</f>
         <v>15617.28</v>
       </c>
-      <c r="T6" s="96" t="n">
+      <c r="T6" s="95" t="n">
         <f aca="false">(K6*Q6)/100</f>
         <v>5205.76</v>
       </c>
-      <c r="W6" s="103"/>
+      <c r="W6" s="3"/>
     </row>
-    <row r="7" s="98" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="88" t="n">
+    <row r="7" s="97" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="86" t="n">
         <v>8</v>
       </c>
       <c r="B7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="90" t="n">
+      <c r="C7" s="88" t="n">
         <v>29</v>
       </c>
-      <c r="D7" s="90" t="n">
+      <c r="D7" s="88" t="n">
         <v>554</v>
       </c>
-      <c r="E7" s="90" t="n">
+      <c r="E7" s="88" t="n">
         <v>510</v>
       </c>
-      <c r="F7" s="90" t="s">
+      <c r="F7" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="90" t="n">
+      <c r="G7" s="88" t="n">
         <v>35.12</v>
       </c>
-      <c r="H7" s="93" t="n">
+      <c r="H7" s="94" t="n">
         <v>1110</v>
       </c>
-      <c r="I7" s="91" t="n">
+      <c r="I7" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J7" s="92" t="n">
+      <c r="J7" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K7" s="93" t="n">
+      <c r="K7" s="91" t="n">
         <f aca="false">(G7*I7)*160</f>
         <v>5900.16</v>
       </c>
-      <c r="L7" s="91" t="n">
+      <c r="L7" s="89" t="n">
         <f aca="false">(K7*P7)/100</f>
         <v>1475.04</v>
       </c>
-      <c r="M7" s="105" t="s">
+      <c r="M7" s="104" t="s">
         <v>42</v>
       </c>
       <c r="N7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O7" s="94" t="s">
+      <c r="O7" s="92" t="s">
         <v>35</v>
       </c>
       <c r="P7" s="28" t="n">
@@ -16751,65 +16747,65 @@
       <c r="R7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="93" t="n">
+      <c r="S7" s="94" t="n">
         <f aca="false">L7</f>
         <v>1475.04</v>
       </c>
-      <c r="T7" s="96" t="n">
+      <c r="T7" s="95" t="n">
         <f aca="false">(K7*Q7)/100</f>
         <v>491.68</v>
       </c>
-      <c r="W7" s="103"/>
+      <c r="W7" s="3"/>
     </row>
-    <row r="8" s="98" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="88" t="n">
+    <row r="8" s="97" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="86" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="106" t="n">
+      <c r="C8" s="105" t="n">
         <v>29</v>
       </c>
-      <c r="D8" s="106" t="n">
+      <c r="D8" s="105" t="n">
         <v>554</v>
       </c>
-      <c r="E8" s="106" t="n">
+      <c r="E8" s="105" t="n">
         <v>518</v>
       </c>
-      <c r="F8" s="106" t="s">
+      <c r="F8" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="106" t="n">
+      <c r="G8" s="105" t="n">
         <v>84.29</v>
       </c>
-      <c r="H8" s="91" t="n">
+      <c r="H8" s="89" t="n">
         <v>2661</v>
       </c>
-      <c r="I8" s="91" t="n">
+      <c r="I8" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J8" s="92" t="n">
+      <c r="J8" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K8" s="93" t="n">
+      <c r="K8" s="91" t="n">
         <f aca="false">(G8*I8)*160</f>
         <v>14160.72</v>
       </c>
-      <c r="L8" s="91" t="n">
+      <c r="L8" s="89" t="n">
         <f aca="false">(K8*P8)/100</f>
         <v>3540.18</v>
       </c>
       <c r="M8" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="107" t="s">
+      <c r="N8" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="108" t="s">
+      <c r="O8" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="107" t="n">
+      <c r="P8" s="106" t="n">
         <f aca="false">(100*2)/8</f>
         <v>25</v>
       </c>
@@ -16817,69 +16813,69 @@
         <f aca="false">P8/3</f>
         <v>8.33333333333333</v>
       </c>
-      <c r="R8" s="107" t="s">
+      <c r="R8" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="S8" s="93" t="n">
+      <c r="S8" s="94" t="n">
         <f aca="false">L8</f>
         <v>3540.18</v>
       </c>
-      <c r="T8" s="96" t="n">
+      <c r="T8" s="95" t="n">
         <f aca="false">(K8*Q8)/100</f>
         <v>1180.06</v>
       </c>
       <c r="U8" s="42"/>
-      <c r="W8" s="0"/>
+      <c r="W8" s="2"/>
     </row>
-    <row r="9" s="98" customFormat="true" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="88" t="n">
+    <row r="9" s="97" customFormat="true" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="86" t="n">
         <v>10</v>
       </c>
-      <c r="B9" s="109" t="s">
+      <c r="B9" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="110" t="n">
+      <c r="C9" s="109" t="n">
         <v>29</v>
       </c>
-      <c r="D9" s="110" t="n">
+      <c r="D9" s="109" t="n">
         <v>554</v>
       </c>
-      <c r="E9" s="110" t="n">
+      <c r="E9" s="109" t="n">
         <v>514</v>
       </c>
-      <c r="F9" s="110" t="s">
+      <c r="F9" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="110" t="n">
+      <c r="G9" s="109" t="n">
         <v>216.91</v>
       </c>
-      <c r="H9" s="91" t="n">
+      <c r="H9" s="89" t="n">
         <v>27333</v>
       </c>
-      <c r="I9" s="91" t="n">
+      <c r="I9" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J9" s="92" t="n">
+      <c r="J9" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K9" s="93" t="n">
+      <c r="K9" s="91" t="n">
         <f aca="false">(G9*I9)*160</f>
         <v>36440.88</v>
       </c>
-      <c r="L9" s="91" t="n">
+      <c r="L9" s="89" t="n">
         <f aca="false">(K9*P9)/100</f>
         <v>36440.88</v>
       </c>
       <c r="M9" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="N9" s="109" t="s">
+      <c r="N9" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="111" t="s">
+      <c r="O9" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="P9" s="109" t="n">
+      <c r="P9" s="108" t="n">
         <f aca="false">(100*1)/1</f>
         <v>100</v>
       </c>
@@ -16887,56 +16883,56 @@
         <f aca="false">P9/3</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="R9" s="109" t="s">
+      <c r="R9" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="S9" s="93" t="n">
+      <c r="S9" s="94" t="n">
         <f aca="false">L9</f>
         <v>36440.88</v>
       </c>
-      <c r="T9" s="96" t="n">
+      <c r="T9" s="95" t="n">
         <f aca="false">(K9*Q9)/100</f>
         <v>12146.96</v>
       </c>
       <c r="U9" s="42"/>
-      <c r="W9" s="103"/>
+      <c r="W9" s="3"/>
     </row>
-    <row r="10" s="98" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="88" t="n">
+    <row r="10" s="97" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="86" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="90" t="n">
+      <c r="C10" s="88" t="n">
         <v>18</v>
       </c>
-      <c r="D10" s="90" t="n">
+      <c r="D10" s="88" t="n">
         <v>176</v>
       </c>
-      <c r="E10" s="90" t="n">
+      <c r="E10" s="88" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="90" t="s">
+      <c r="F10" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="90" t="n">
+      <c r="G10" s="88" t="n">
         <v>198.84</v>
       </c>
-      <c r="H10" s="91" t="n">
+      <c r="H10" s="89" t="n">
         <v>8352</v>
       </c>
-      <c r="I10" s="91" t="n">
+      <c r="I10" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J10" s="92" t="n">
+      <c r="J10" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K10" s="93" t="n">
+      <c r="K10" s="91" t="n">
         <f aca="false">(G10*I10)*160</f>
         <v>33405.12</v>
       </c>
-      <c r="L10" s="91" t="n">
+      <c r="L10" s="89" t="n">
         <f aca="false">(K10*P10)/100</f>
         <v>11135.04</v>
       </c>
@@ -16946,10 +16942,10 @@
       <c r="N10" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="94" t="s">
+      <c r="O10" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="112" t="n">
+      <c r="P10" s="111" t="n">
         <f aca="false">(100*1)/3</f>
         <v>33.3333333333333</v>
       </c>
@@ -16960,52 +16956,52 @@
       <c r="R10" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="S10" s="93" t="n">
+      <c r="S10" s="94" t="n">
         <f aca="false">L10</f>
         <v>11135.04</v>
       </c>
-      <c r="T10" s="96" t="n">
+      <c r="T10" s="95" t="n">
         <f aca="false">(K10*Q10)/100</f>
         <v>3711.68</v>
       </c>
-      <c r="W10" s="0"/>
+      <c r="W10" s="2"/>
     </row>
-    <row r="11" s="98" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="88" t="n">
+    <row r="11" s="97" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="86" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="90" t="n">
+      <c r="C11" s="88" t="n">
         <v>31</v>
       </c>
-      <c r="D11" s="90" t="n">
+      <c r="D11" s="88" t="n">
         <v>162</v>
       </c>
-      <c r="E11" s="90" t="n">
+      <c r="E11" s="88" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="90" t="s">
+      <c r="F11" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="90" t="n">
+      <c r="G11" s="88" t="n">
         <v>542.28</v>
       </c>
-      <c r="H11" s="91" t="n">
+      <c r="H11" s="89" t="n">
         <v>34164</v>
       </c>
-      <c r="I11" s="91" t="n">
+      <c r="I11" s="89" t="n">
         <v>1.05</v>
       </c>
-      <c r="J11" s="92" t="n">
+      <c r="J11" s="90" t="n">
         <v>160</v>
       </c>
-      <c r="K11" s="93" t="n">
+      <c r="K11" s="91" t="n">
         <f aca="false">(G11*I11)*160</f>
         <v>91103.04</v>
       </c>
-      <c r="L11" s="91" t="n">
+      <c r="L11" s="89" t="n">
         <f aca="false">(K11*P11)/100</f>
         <v>45551.52</v>
       </c>
@@ -17015,10 +17011,10 @@
       <c r="N11" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="94" t="s">
+      <c r="O11" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="112" t="n">
+      <c r="P11" s="111" t="n">
         <f aca="false">(100*1)/2</f>
         <v>50</v>
       </c>
@@ -17029,154 +17025,153 @@
       <c r="R11" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="S11" s="93" t="n">
+      <c r="S11" s="94" t="n">
         <f aca="false">L11</f>
         <v>45551.52</v>
       </c>
-      <c r="T11" s="96" t="n">
+      <c r="T11" s="95" t="n">
         <f aca="false">(K11*Q11)/100</f>
         <v>15183.84</v>
       </c>
-      <c r="U11" s="102"/>
-      <c r="W11" s="0"/>
+      <c r="W11" s="2"/>
     </row>
-    <row r="12" s="98" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="88" t="n">
+    <row r="12" s="97" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="113" t="s">
+      <c r="B12" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="114" t="n">
+      <c r="C12" s="113" t="n">
         <v>48</v>
       </c>
-      <c r="D12" s="114" t="n">
+      <c r="D12" s="113" t="n">
         <v>49</v>
       </c>
-      <c r="E12" s="114" t="n">
+      <c r="E12" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="114" t="s">
+      <c r="F12" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="114" t="n">
+      <c r="G12" s="113" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="115" t="n">
+      <c r="H12" s="114" t="n">
         <v>3000</v>
       </c>
-      <c r="I12" s="115" t="n">
+      <c r="I12" s="114" t="n">
         <v>1.05</v>
       </c>
-      <c r="J12" s="116" t="n">
+      <c r="J12" s="115" t="n">
         <v>160</v>
       </c>
-      <c r="K12" s="117" t="n">
+      <c r="K12" s="116" t="n">
         <v>3000</v>
       </c>
-      <c r="L12" s="115" t="n">
+      <c r="L12" s="114" t="n">
         <f aca="false">K12</f>
         <v>3000</v>
       </c>
-      <c r="M12" s="113" t="s">
+      <c r="M12" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="N12" s="113" t="s">
+      <c r="N12" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="O12" s="118" t="s">
+      <c r="O12" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="119" t="n">
+      <c r="P12" s="118" t="n">
         <f aca="false">(100*3)/6</f>
         <v>50</v>
       </c>
-      <c r="Q12" s="120" t="n">
+      <c r="Q12" s="119" t="n">
         <f aca="false">P12/3</f>
         <v>16.6666666666667</v>
       </c>
-      <c r="R12" s="113" t="s">
+      <c r="R12" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="S12" s="93" t="n">
+      <c r="S12" s="94" t="n">
         <f aca="false">L12</f>
         <v>3000</v>
       </c>
-      <c r="T12" s="96" t="n">
+      <c r="T12" s="95" t="n">
         <f aca="false">(K12*Q12)/100</f>
         <v>500.000000000001</v>
       </c>
-      <c r="W12" s="0"/>
+      <c r="W12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="91" t="n">
+      <c r="E13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="89" t="n">
         <f aca="false">SUM(H2:H12)</f>
         <v>96817</v>
       </c>
-      <c r="K13" s="91" t="n">
+      <c r="K13" s="89" t="n">
         <f aca="false">SUM(K2:K12)</f>
         <v>242360.2</v>
       </c>
-      <c r="L13" s="91" t="n">
+      <c r="L13" s="89" t="n">
         <f aca="false">SUM(L2:L12)</f>
         <v>127443.19</v>
       </c>
-      <c r="Q13" s="102"/>
-      <c r="S13" s="91" t="n">
+      <c r="Q13" s="97"/>
+      <c r="S13" s="89" t="n">
         <f aca="false">SUM(S2:S12)</f>
         <v>127443.19</v>
       </c>
-      <c r="T13" s="122" t="n">
+      <c r="T13" s="121" t="n">
         <f aca="false">SUM(T2:T12)</f>
         <v>41981.0633333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="Q14" s="102"/>
+      <c r="E14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="Q14" s="97"/>
     </row>
     <row r="15" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="123"/>
-      <c r="S15" s="124"/>
-      <c r="T15" s="125"/>
+      <c r="E15" s="120"/>
+      <c r="G15" s="120"/>
+      <c r="Q15" s="97"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="124"/>
     </row>
     <row r="16" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="Q16" s="102"/>
-      <c r="R16" s="123"/>
+      <c r="E16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="Q16" s="97"/>
+      <c r="R16" s="122"/>
     </row>
     <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="Q17" s="102"/>
+      <c r="E17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="Q17" s="97"/>
     </row>
     <row r="18" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="127" t="n">
+      <c r="C18" s="126" t="n">
         <v>29</v>
       </c>
-      <c r="D18" s="127" t="n">
+      <c r="D18" s="126" t="n">
         <v>554</v>
       </c>
-      <c r="E18" s="128" t="n">
+      <c r="E18" s="127" t="n">
         <v>513</v>
       </c>
-      <c r="F18" s="127" t="s">
+      <c r="F18" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="128" t="n">
+      <c r="G18" s="127" t="n">
         <v>216.91</v>
       </c>
       <c r="M18" s="63" t="s">
@@ -17191,17 +17186,17 @@
       <c r="P18" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="Q18" s="102"/>
+      <c r="Q18" s="97"/>
     </row>
     <row r="19" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="128"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="127"/>
       <c r="M19" s="63"/>
       <c r="N19" s="63" t="s">
         <v>63</v>
@@ -17212,25 +17207,25 @@
       <c r="P19" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="Q19" s="102"/>
+      <c r="Q19" s="97"/>
     </row>
     <row r="20" customFormat="false" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="129" t="n">
+      <c r="C20" s="128" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="129" t="n">
+      <c r="D20" s="128" t="n">
         <v>554</v>
       </c>
-      <c r="E20" s="128" t="n">
+      <c r="E20" s="127" t="n">
         <v>504</v>
       </c>
-      <c r="F20" s="129" t="s">
+      <c r="F20" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="129" t="n">
+      <c r="G20" s="128" t="n">
         <v>247.9</v>
       </c>
       <c r="M20" s="66" t="s">
@@ -17245,25 +17240,25 @@
       <c r="P20" s="63" t="n">
         <v>100</v>
       </c>
-      <c r="Q20" s="102"/>
+      <c r="Q20" s="97"/>
     </row>
     <row r="21" customFormat="false" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="130" t="n">
+      <c r="C21" s="129" t="n">
         <v>29</v>
       </c>
-      <c r="D21" s="130" t="n">
+      <c r="D21" s="129" t="n">
         <v>554</v>
       </c>
-      <c r="E21" s="131" t="n">
+      <c r="E21" s="130" t="n">
         <v>505</v>
       </c>
-      <c r="F21" s="130" t="s">
+      <c r="F21" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="130" t="n">
+      <c r="G21" s="129" t="n">
         <v>92.06</v>
       </c>
       <c r="M21" s="72" t="s">
@@ -17283,19 +17278,19 @@
       <c r="B23" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="130" t="n">
+      <c r="C23" s="129" t="n">
         <v>29</v>
       </c>
-      <c r="D23" s="130" t="n">
+      <c r="D23" s="129" t="n">
         <v>554</v>
       </c>
-      <c r="E23" s="131" t="n">
+      <c r="E23" s="130" t="n">
         <v>512</v>
       </c>
-      <c r="F23" s="130" t="s">
+      <c r="F23" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="132" t="s">
+      <c r="G23" s="131" t="s">
         <v>65</v>
       </c>
       <c r="M23" s="75" t="s">
@@ -17306,10 +17301,10 @@
       <c r="P23" s="69"/>
     </row>
     <row r="24" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="121"/>
-      <c r="G24" s="121"/>
+      <c r="E24" s="120"/>
+      <c r="G24" s="120"/>
       <c r="O24" s="41"/>
-      <c r="Q24" s="102"/>
+      <c r="Q24" s="97"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
